--- a/artfynd/A 39183-2026 artfynd.xlsx
+++ b/artfynd/A 39183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857971</v>
       </c>
       <c r="B2" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858004</v>
       </c>
       <c r="B3" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136857976</v>
       </c>
       <c r="B4" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136857962</v>
       </c>
       <c r="B5" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39183-2026 artfynd.xlsx
+++ b/artfynd/A 39183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857971</v>
       </c>
       <c r="B2" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858004</v>
       </c>
       <c r="B3" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136857976</v>
       </c>
       <c r="B4" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136857962</v>
       </c>
       <c r="B5" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39183-2026 artfynd.xlsx
+++ b/artfynd/A 39183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857971</v>
       </c>
       <c r="B2" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858004</v>
       </c>
       <c r="B3" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136857976</v>
       </c>
       <c r="B4" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136857962</v>
       </c>
       <c r="B5" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39183-2026 artfynd.xlsx
+++ b/artfynd/A 39183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857971</v>
       </c>
       <c r="B2" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136857962</v>
       </c>
       <c r="B5" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39183-2026 artfynd.xlsx
+++ b/artfynd/A 39183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857971</v>
       </c>
       <c r="B2" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858004</v>
       </c>
       <c r="B3" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136857976</v>
       </c>
       <c r="B4" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136857962</v>
       </c>
       <c r="B5" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39183-2026 artfynd.xlsx
+++ b/artfynd/A 39183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857971</v>
       </c>
       <c r="B2" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858004</v>
       </c>
       <c r="B3" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136857976</v>
       </c>
       <c r="B4" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136857962</v>
       </c>
       <c r="B5" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39183-2026 artfynd.xlsx
+++ b/artfynd/A 39183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857971</v>
       </c>
       <c r="B2" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858004</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136857976</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136857962</v>
       </c>
       <c r="B5" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39183-2026 artfynd.xlsx
+++ b/artfynd/A 39183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857971</v>
       </c>
       <c r="B2" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858004</v>
       </c>
       <c r="B3" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136857976</v>
       </c>
       <c r="B4" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136857962</v>
       </c>
       <c r="B5" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39183-2026 artfynd.xlsx
+++ b/artfynd/A 39183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857971</v>
       </c>
       <c r="B2" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136857962</v>
       </c>
       <c r="B5" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39183-2026 artfynd.xlsx
+++ b/artfynd/A 39183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857971</v>
       </c>
       <c r="B2" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858004</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136857976</v>
       </c>
       <c r="B4" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136857962</v>
       </c>
       <c r="B5" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39183-2026 artfynd.xlsx
+++ b/artfynd/A 39183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857971</v>
       </c>
       <c r="B2" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136857962</v>
       </c>
       <c r="B5" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39183-2026 artfynd.xlsx
+++ b/artfynd/A 39183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857971</v>
       </c>
       <c r="B2" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858004</v>
       </c>
       <c r="B3" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136857976</v>
       </c>
       <c r="B4" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136857962</v>
       </c>
       <c r="B5" t="n">
-        <v>93448</v>
+        <v>93453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39183-2026 artfynd.xlsx
+++ b/artfynd/A 39183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857971</v>
       </c>
       <c r="B2" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136857962</v>
       </c>
       <c r="B5" t="n">
-        <v>93453</v>
+        <v>93455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39183-2026 artfynd.xlsx
+++ b/artfynd/A 39183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857971</v>
       </c>
       <c r="B2" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858004</v>
       </c>
       <c r="B3" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136857976</v>
       </c>
       <c r="B4" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136857962</v>
       </c>
       <c r="B5" t="n">
-        <v>93455</v>
+        <v>93461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39183-2026 artfynd.xlsx
+++ b/artfynd/A 39183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857971</v>
       </c>
       <c r="B2" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858004</v>
       </c>
       <c r="B3" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136857976</v>
       </c>
       <c r="B4" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136857962</v>
       </c>
       <c r="B5" t="n">
-        <v>93461</v>
+        <v>93473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
